--- a/raw_data/capex_capacity.xlsx
+++ b/raw_data/capex_capacity.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1d83fea8a85e4500/Documents/JJE/RS/biogas-upgrading-project/clean_data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/1d83fea8a85e4500/Documents/JJE/RS/biogas-upgrading-project/raw_data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_31A510B9D370D67C6523C7F0505ED87656CD741A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{7F88D81C-C60B-42BF-88C4-E021D62DA2DF}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_31A510B9D370D67C6523C7F0505ED87656CD741A" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94697447-4366-4B92-BE4F-BAEAB3B30A41}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2892" yWindow="2892" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -441,6 +441,13 @@
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="54.21875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="21" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.3">
